--- a/output/Data and Chart Outputs/south_america_power_by_type.xlsx
+++ b/output/Data and Chart Outputs/south_america_power_by_type.xlsx
@@ -171,6 +171,7 @@
           </a:p>
         </rich>
       </tx>
+      <overlay val="0"/>
     </title>
     <plotArea>
       <barChart>
@@ -383,7 +384,7 @@
           <orientation val="minMax"/>
         </scaling>
         <delete val="0"/>
-        <axPos val="l"/>
+        <axPos val="b"/>
         <numFmt formatCode="mmm/yy" sourceLinked="0"/>
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
@@ -415,6 +416,7 @@
               </a:p>
             </rich>
           </tx>
+          <overlay val="0"/>
         </title>
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
@@ -423,6 +425,7 @@
     </plotArea>
     <legend>
       <legendPos val="b"/>
+      <overlay val="0"/>
     </legend>
     <plotVisOnly val="1"/>
     <dispBlanksAs val="gap"/>
@@ -453,6 +456,7 @@
           </a:p>
         </rich>
       </tx>
+      <overlay val="0"/>
     </title>
     <plotArea>
       <barChart>
@@ -665,7 +669,7 @@
           <orientation val="minMax"/>
         </scaling>
         <delete val="0"/>
-        <axPos val="l"/>
+        <axPos val="b"/>
         <numFmt formatCode="mmm/yy" sourceLinked="0"/>
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
@@ -697,6 +701,7 @@
               </a:p>
             </rich>
           </tx>
+          <overlay val="0"/>
         </title>
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
@@ -705,6 +710,7 @@
     </plotArea>
     <legend>
       <legendPos val="b"/>
+      <overlay val="0"/>
     </legend>
     <plotVisOnly val="1"/>
     <dispBlanksAs val="gap"/>
@@ -735,6 +741,7 @@
           </a:p>
         </rich>
       </tx>
+      <overlay val="0"/>
     </title>
     <plotArea>
       <barChart>
@@ -947,7 +954,7 @@
           <orientation val="minMax"/>
         </scaling>
         <delete val="0"/>
-        <axPos val="l"/>
+        <axPos val="b"/>
         <numFmt formatCode="mmm/yy" sourceLinked="0"/>
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
@@ -979,6 +986,7 @@
               </a:p>
             </rich>
           </tx>
+          <overlay val="0"/>
         </title>
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
@@ -987,6 +995,7 @@
     </plotArea>
     <legend>
       <legendPos val="b"/>
+      <overlay val="0"/>
     </legend>
     <plotVisOnly val="1"/>
     <dispBlanksAs val="gap"/>
@@ -1017,6 +1026,7 @@
           </a:p>
         </rich>
       </tx>
+      <overlay val="0"/>
     </title>
     <plotArea>
       <barChart>
@@ -1229,7 +1239,7 @@
           <orientation val="minMax"/>
         </scaling>
         <delete val="0"/>
-        <axPos val="l"/>
+        <axPos val="b"/>
         <numFmt formatCode="mmm/yy" sourceLinked="0"/>
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
@@ -1261,6 +1271,7 @@
               </a:p>
             </rich>
           </tx>
+          <overlay val="0"/>
         </title>
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
@@ -1269,6 +1280,7 @@
     </plotArea>
     <legend>
       <legendPos val="b"/>
+      <overlay val="0"/>
     </legend>
     <plotVisOnly val="1"/>
     <dispBlanksAs val="gap"/>
@@ -1299,6 +1311,7 @@
           </a:p>
         </rich>
       </tx>
+      <overlay val="0"/>
     </title>
     <plotArea>
       <barChart>
@@ -1511,7 +1524,7 @@
           <orientation val="minMax"/>
         </scaling>
         <delete val="0"/>
-        <axPos val="l"/>
+        <axPos val="b"/>
         <numFmt formatCode="mmm/yy" sourceLinked="0"/>
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
@@ -1543,6 +1556,7 @@
               </a:p>
             </rich>
           </tx>
+          <overlay val="0"/>
         </title>
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
@@ -1551,6 +1565,7 @@
     </plotArea>
     <legend>
       <legendPos val="b"/>
+      <overlay val="0"/>
     </legend>
     <plotVisOnly val="1"/>
     <dispBlanksAs val="gap"/>
@@ -1581,6 +1596,7 @@
           </a:p>
         </rich>
       </tx>
+      <overlay val="0"/>
     </title>
     <plotArea>
       <barChart>
@@ -1793,7 +1809,7 @@
           <orientation val="minMax"/>
         </scaling>
         <delete val="0"/>
-        <axPos val="l"/>
+        <axPos val="b"/>
         <numFmt formatCode="mmm/yy" sourceLinked="0"/>
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
@@ -1825,6 +1841,7 @@
               </a:p>
             </rich>
           </tx>
+          <overlay val="0"/>
         </title>
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
@@ -1833,6 +1850,7 @@
     </plotArea>
     <legend>
       <legendPos val="b"/>
+      <overlay val="0"/>
     </legend>
     <plotVisOnly val="1"/>
     <dispBlanksAs val="gap"/>
@@ -1863,6 +1881,7 @@
           </a:p>
         </rich>
       </tx>
+      <overlay val="0"/>
     </title>
     <plotArea>
       <barChart>
@@ -2075,7 +2094,7 @@
           <orientation val="minMax"/>
         </scaling>
         <delete val="0"/>
-        <axPos val="l"/>
+        <axPos val="b"/>
         <numFmt formatCode="mmm/yy" sourceLinked="0"/>
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
@@ -2107,6 +2126,7 @@
               </a:p>
             </rich>
           </tx>
+          <overlay val="0"/>
         </title>
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
@@ -2115,6 +2135,7 @@
     </plotArea>
     <legend>
       <legendPos val="b"/>
+      <overlay val="0"/>
     </legend>
     <plotVisOnly val="1"/>
     <dispBlanksAs val="gap"/>
@@ -2145,6 +2166,7 @@
           </a:p>
         </rich>
       </tx>
+      <overlay val="0"/>
     </title>
     <plotArea>
       <barChart>
@@ -2357,7 +2379,7 @@
           <orientation val="minMax"/>
         </scaling>
         <delete val="0"/>
-        <axPos val="l"/>
+        <axPos val="b"/>
         <numFmt formatCode="mmm/yy" sourceLinked="0"/>
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
@@ -2389,6 +2411,7 @@
               </a:p>
             </rich>
           </tx>
+          <overlay val="0"/>
         </title>
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
@@ -2397,6 +2420,7 @@
     </plotArea>
     <legend>
       <legendPos val="b"/>
+      <overlay val="0"/>
     </legend>
     <plotVisOnly val="1"/>
     <dispBlanksAs val="gap"/>

--- a/output/Data and Chart Outputs/south_america_power_by_type.xlsx
+++ b/output/Data and Chart Outputs/south_america_power_by_type.xlsx
@@ -32,8 +32,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="mmm/yy"/>
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
+    <numFmt numFmtId="165" formatCode="mmm/yy"/>
   </numFmts>
   <fonts count="2">
     <font>
@@ -73,11 +74,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -389,6 +389,18 @@
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
         <tickLblPos val="low"/>
+        <txPr>
+          <a:bodyPr rot="-2700000" vert="horz"/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:t/>
+            </a:r>
+            <a:endParaRPr/>
+          </a:p>
+        </txPr>
         <crossAx val="100"/>
         <lblOffset val="100"/>
         <tickLblSkip val="5"/>
@@ -422,6 +434,12 @@
         <minorTickMark val="none"/>
         <crossAx val="10"/>
       </valAx>
+      <spPr>
+        <a:ln>
+          <a:noFill/>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
     </plotArea>
     <legend>
       <legendPos val="b"/>
@@ -674,6 +692,18 @@
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
         <tickLblPos val="low"/>
+        <txPr>
+          <a:bodyPr rot="-2700000" vert="horz"/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:t/>
+            </a:r>
+            <a:endParaRPr/>
+          </a:p>
+        </txPr>
         <crossAx val="100"/>
         <lblOffset val="100"/>
         <tickLblSkip val="5"/>
@@ -707,6 +737,12 @@
         <minorTickMark val="none"/>
         <crossAx val="10"/>
       </valAx>
+      <spPr>
+        <a:ln>
+          <a:noFill/>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
     </plotArea>
     <legend>
       <legendPos val="b"/>
@@ -959,6 +995,18 @@
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
         <tickLblPos val="low"/>
+        <txPr>
+          <a:bodyPr rot="-2700000" vert="horz"/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:t/>
+            </a:r>
+            <a:endParaRPr/>
+          </a:p>
+        </txPr>
         <crossAx val="100"/>
         <lblOffset val="100"/>
         <tickLblSkip val="5"/>
@@ -992,6 +1040,12 @@
         <minorTickMark val="none"/>
         <crossAx val="10"/>
       </valAx>
+      <spPr>
+        <a:ln>
+          <a:noFill/>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
     </plotArea>
     <legend>
       <legendPos val="b"/>
@@ -1244,6 +1298,18 @@
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
         <tickLblPos val="low"/>
+        <txPr>
+          <a:bodyPr rot="-2700000" vert="horz"/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:t/>
+            </a:r>
+            <a:endParaRPr/>
+          </a:p>
+        </txPr>
         <crossAx val="100"/>
         <lblOffset val="100"/>
         <tickLblSkip val="5"/>
@@ -1277,6 +1343,12 @@
         <minorTickMark val="none"/>
         <crossAx val="10"/>
       </valAx>
+      <spPr>
+        <a:ln>
+          <a:noFill/>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
     </plotArea>
     <legend>
       <legendPos val="b"/>
@@ -1529,6 +1601,18 @@
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
         <tickLblPos val="low"/>
+        <txPr>
+          <a:bodyPr rot="-2700000" vert="horz"/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:t/>
+            </a:r>
+            <a:endParaRPr/>
+          </a:p>
+        </txPr>
         <crossAx val="100"/>
         <lblOffset val="100"/>
         <tickLblSkip val="5"/>
@@ -1562,6 +1646,12 @@
         <minorTickMark val="none"/>
         <crossAx val="10"/>
       </valAx>
+      <spPr>
+        <a:ln>
+          <a:noFill/>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
     </plotArea>
     <legend>
       <legendPos val="b"/>
@@ -1814,6 +1904,18 @@
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
         <tickLblPos val="low"/>
+        <txPr>
+          <a:bodyPr rot="-2700000" vert="horz"/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:t/>
+            </a:r>
+            <a:endParaRPr/>
+          </a:p>
+        </txPr>
         <crossAx val="100"/>
         <lblOffset val="100"/>
         <tickLblSkip val="5"/>
@@ -1847,6 +1949,12 @@
         <minorTickMark val="none"/>
         <crossAx val="10"/>
       </valAx>
+      <spPr>
+        <a:ln>
+          <a:noFill/>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
     </plotArea>
     <legend>
       <legendPos val="b"/>
@@ -2099,6 +2207,18 @@
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
         <tickLblPos val="low"/>
+        <txPr>
+          <a:bodyPr rot="-2700000" vert="horz"/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:t/>
+            </a:r>
+            <a:endParaRPr/>
+          </a:p>
+        </txPr>
         <crossAx val="100"/>
         <lblOffset val="100"/>
         <tickLblSkip val="5"/>
@@ -2132,6 +2252,12 @@
         <minorTickMark val="none"/>
         <crossAx val="10"/>
       </valAx>
+      <spPr>
+        <a:ln>
+          <a:noFill/>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
     </plotArea>
     <legend>
       <legendPos val="b"/>
@@ -2384,6 +2510,18 @@
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
         <tickLblPos val="low"/>
+        <txPr>
+          <a:bodyPr rot="-2700000" vert="horz"/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:t/>
+            </a:r>
+            <a:endParaRPr/>
+          </a:p>
+        </txPr>
         <crossAx val="100"/>
         <lblOffset val="100"/>
         <tickLblSkip val="5"/>
@@ -2417,6 +2555,12 @@
         <minorTickMark val="none"/>
         <crossAx val="10"/>
       </valAx>
+      <spPr>
+        <a:ln>
+          <a:noFill/>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
     </plotArea>
     <legend>
       <legendPos val="b"/>
@@ -2973,6 +3117,7 @@
         </is>
       </c>
     </row>
+    <row r="5"/>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
@@ -2987,6 +3132,7 @@
         </is>
       </c>
     </row>
+    <row r="8"/>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
@@ -21952,7 +22098,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="3" t="n">
+      <c r="A2" s="2" t="n">
         <v>44197</v>
       </c>
       <c r="B2" t="n">
@@ -21978,7 +22124,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="n">
+      <c r="A3" s="2" t="n">
         <v>44228</v>
       </c>
       <c r="B3" t="n">
@@ -22004,7 +22150,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="3" t="n">
+      <c r="A4" s="2" t="n">
         <v>44256</v>
       </c>
       <c r="B4" t="n">
@@ -22030,7 +22176,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="3" t="n">
+      <c r="A5" s="2" t="n">
         <v>44287</v>
       </c>
       <c r="B5" t="n">
@@ -22056,7 +22202,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="3" t="n">
+      <c r="A6" s="2" t="n">
         <v>44317</v>
       </c>
       <c r="B6" t="n">
@@ -22082,7 +22228,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="3" t="n">
+      <c r="A7" s="2" t="n">
         <v>44348</v>
       </c>
       <c r="B7" t="n">
@@ -22108,7 +22254,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="3" t="n">
+      <c r="A8" s="2" t="n">
         <v>44378</v>
       </c>
       <c r="B8" t="n">
@@ -22134,7 +22280,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="3" t="n">
+      <c r="A9" s="2" t="n">
         <v>44409</v>
       </c>
       <c r="B9" t="n">
@@ -22160,7 +22306,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="3" t="n">
+      <c r="A10" s="2" t="n">
         <v>44440</v>
       </c>
       <c r="B10" t="n">
@@ -22186,7 +22332,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="3" t="n">
+      <c r="A11" s="2" t="n">
         <v>44470</v>
       </c>
       <c r="B11" t="n">
@@ -22212,7 +22358,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="3" t="n">
+      <c r="A12" s="2" t="n">
         <v>44501</v>
       </c>
       <c r="B12" t="n">
@@ -22238,7 +22384,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="3" t="n">
+      <c r="A13" s="2" t="n">
         <v>44531</v>
       </c>
       <c r="B13" t="n">
@@ -22264,7 +22410,7 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="3" t="n">
+      <c r="A14" s="2" t="n">
         <v>44562</v>
       </c>
       <c r="B14" t="n">
@@ -22290,7 +22436,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="3" t="n">
+      <c r="A15" s="2" t="n">
         <v>44593</v>
       </c>
       <c r="B15" t="n">
@@ -22316,7 +22462,7 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="3" t="n">
+      <c r="A16" s="2" t="n">
         <v>44621</v>
       </c>
       <c r="B16" t="n">
@@ -22342,7 +22488,7 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="3" t="n">
+      <c r="A17" s="2" t="n">
         <v>44652</v>
       </c>
       <c r="B17" t="n">
@@ -22368,7 +22514,7 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="3" t="n">
+      <c r="A18" s="2" t="n">
         <v>44682</v>
       </c>
       <c r="B18" t="n">
@@ -22394,7 +22540,7 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="3" t="n">
+      <c r="A19" s="2" t="n">
         <v>44713</v>
       </c>
       <c r="B19" t="n">
@@ -22420,7 +22566,7 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="3" t="n">
+      <c r="A20" s="2" t="n">
         <v>44743</v>
       </c>
       <c r="B20" t="n">
@@ -22446,7 +22592,7 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="3" t="n">
+      <c r="A21" s="2" t="n">
         <v>44774</v>
       </c>
       <c r="B21" t="n">
@@ -22472,7 +22618,7 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="3" t="n">
+      <c r="A22" s="2" t="n">
         <v>44805</v>
       </c>
       <c r="B22" t="n">
@@ -22498,7 +22644,7 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="3" t="n">
+      <c r="A23" s="2" t="n">
         <v>44835</v>
       </c>
       <c r="B23" t="n">
@@ -22524,7 +22670,7 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="3" t="n">
+      <c r="A24" s="2" t="n">
         <v>44866</v>
       </c>
       <c r="B24" t="n">
@@ -22550,7 +22696,7 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="3" t="n">
+      <c r="A25" s="2" t="n">
         <v>44896</v>
       </c>
       <c r="B25" t="n">
@@ -22576,7 +22722,7 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="3" t="n">
+      <c r="A26" s="2" t="n">
         <v>44927</v>
       </c>
       <c r="B26" t="n">
@@ -22602,7 +22748,7 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="3" t="n">
+      <c r="A27" s="2" t="n">
         <v>44958</v>
       </c>
       <c r="B27" t="n">
@@ -22628,7 +22774,7 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="3" t="n">
+      <c r="A28" s="2" t="n">
         <v>44986</v>
       </c>
       <c r="B28" t="n">
@@ -22654,7 +22800,7 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="3" t="n">
+      <c r="A29" s="2" t="n">
         <v>45017</v>
       </c>
       <c r="B29" t="n">
@@ -22680,7 +22826,7 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="3" t="n">
+      <c r="A30" s="2" t="n">
         <v>45047</v>
       </c>
       <c r="B30" t="n">
@@ -22706,7 +22852,7 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="3" t="n">
+      <c r="A31" s="2" t="n">
         <v>45078</v>
       </c>
       <c r="B31" t="n">
@@ -22732,7 +22878,7 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="3" t="n">
+      <c r="A32" s="2" t="n">
         <v>45108</v>
       </c>
       <c r="B32" t="n">
@@ -22758,7 +22904,7 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="3" t="n">
+      <c r="A33" s="2" t="n">
         <v>45139</v>
       </c>
       <c r="B33" t="n">
@@ -22784,7 +22930,7 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="3" t="n">
+      <c r="A34" s="2" t="n">
         <v>45170</v>
       </c>
       <c r="B34" t="n">
@@ -22810,7 +22956,7 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="3" t="n">
+      <c r="A35" s="2" t="n">
         <v>45200</v>
       </c>
       <c r="B35" t="n">
@@ -22836,7 +22982,7 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="3" t="n">
+      <c r="A36" s="2" t="n">
         <v>45231</v>
       </c>
       <c r="B36" t="n">
@@ -22862,7 +23008,7 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="3" t="n">
+      <c r="A37" s="2" t="n">
         <v>45261</v>
       </c>
       <c r="B37" t="n">
@@ -22888,7 +23034,7 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="3" t="n">
+      <c r="A38" s="2" t="n">
         <v>45292</v>
       </c>
       <c r="B38" t="n">
@@ -22914,7 +23060,7 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="3" t="n">
+      <c r="A39" s="2" t="n">
         <v>45323</v>
       </c>
       <c r="B39" t="n">
@@ -22940,7 +23086,7 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="3" t="n">
+      <c r="A40" s="2" t="n">
         <v>45352</v>
       </c>
       <c r="B40" t="n">
@@ -22966,7 +23112,7 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="3" t="n">
+      <c r="A41" s="2" t="n">
         <v>45383</v>
       </c>
       <c r="B41" t="n">
@@ -22992,7 +23138,7 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="3" t="n">
+      <c r="A42" s="2" t="n">
         <v>45413</v>
       </c>
       <c r="B42" t="n">
@@ -23018,7 +23164,7 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="3" t="n">
+      <c r="A43" s="2" t="n">
         <v>45444</v>
       </c>
       <c r="B43" t="n">
@@ -23044,7 +23190,7 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="3" t="n">
+      <c r="A44" s="2" t="n">
         <v>45474</v>
       </c>
       <c r="B44" t="n">
@@ -23070,7 +23216,7 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="3" t="n">
+      <c r="A45" s="2" t="n">
         <v>45505</v>
       </c>
       <c r="B45" t="n">
@@ -23096,7 +23242,7 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="3" t="n">
+      <c r="A46" s="2" t="n">
         <v>45536</v>
       </c>
       <c r="B46" t="n">
@@ -23122,7 +23268,7 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="3" t="n">
+      <c r="A47" s="2" t="n">
         <v>45566</v>
       </c>
       <c r="B47" t="n">
@@ -23148,7 +23294,7 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="3" t="n">
+      <c r="A48" s="2" t="n">
         <v>45597</v>
       </c>
       <c r="B48" t="n">
@@ -23174,7 +23320,7 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="3" t="n">
+      <c r="A49" s="2" t="n">
         <v>45627</v>
       </c>
       <c r="B49" t="n">
@@ -23200,7 +23346,7 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="3" t="n">
+      <c r="A50" s="2" t="n">
         <v>45658</v>
       </c>
       <c r="B50" t="n">
@@ -23226,7 +23372,7 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="3" t="n">
+      <c r="A51" s="2" t="n">
         <v>45689</v>
       </c>
       <c r="B51" t="n">
@@ -23252,7 +23398,7 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="3" t="n">
+      <c r="A52" s="2" t="n">
         <v>45717</v>
       </c>
       <c r="B52" t="n">
@@ -23278,7 +23424,7 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="3" t="n">
+      <c r="A53" s="2" t="n">
         <v>45748</v>
       </c>
       <c r="B53" t="n">
@@ -23304,7 +23450,7 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="3" t="n">
+      <c r="A54" s="2" t="n">
         <v>45778</v>
       </c>
       <c r="B54" t="n">
@@ -23330,7 +23476,7 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="3" t="n">
+      <c r="A55" s="2" t="n">
         <v>45809</v>
       </c>
       <c r="B55" t="n">
@@ -23356,7 +23502,7 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="3" t="n">
+      <c r="A56" s="2" t="n">
         <v>45839</v>
       </c>
       <c r="B56" t="n">
@@ -23382,7 +23528,7 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="3" t="n">
+      <c r="A57" s="2" t="n">
         <v>45870</v>
       </c>
       <c r="B57" t="n">
@@ -23408,7 +23554,7 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="3" t="n">
+      <c r="A58" s="2" t="n">
         <v>45901</v>
       </c>
       <c r="B58" t="n">
@@ -23434,7 +23580,7 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="3" t="n">
+      <c r="A59" s="2" t="n">
         <v>45931</v>
       </c>
       <c r="B59" t="n">
@@ -23460,7 +23606,7 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="3" t="n">
+      <c r="A60" s="2" t="n">
         <v>45962</v>
       </c>
       <c r="B60" t="n">
@@ -23486,7 +23632,7 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="3" t="n">
+      <c r="A61" s="2" t="n">
         <v>45992</v>
       </c>
       <c r="B61" t="n">
@@ -23512,7 +23658,7 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="3" t="n">
+      <c r="A62" s="2" t="n">
         <v>46023</v>
       </c>
       <c r="B62" t="n">
@@ -23538,7 +23684,7 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="3" t="n">
+      <c r="A63" s="2" t="n">
         <v>46054</v>
       </c>
       <c r="B63" t="n">
@@ -23564,7 +23710,7 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="3" t="n">
+      <c r="A64" s="2" t="n">
         <v>46082</v>
       </c>
       <c r="B64" t="n">
@@ -23590,7 +23736,7 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="3" t="n">
+      <c r="A65" s="2" t="n">
         <v>46113</v>
       </c>
       <c r="B65" t="n">
@@ -23616,7 +23762,7 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="3" t="n">
+      <c r="A66" s="2" t="n">
         <v>46143</v>
       </c>
       <c r="B66" t="n">
@@ -23702,7 +23848,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="3" t="n">
+      <c r="A2" s="2" t="n">
         <v>44197</v>
       </c>
       <c r="B2" t="n">
@@ -23728,7 +23874,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="n">
+      <c r="A3" s="2" t="n">
         <v>44228</v>
       </c>
       <c r="B3" t="n">
@@ -23754,7 +23900,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="3" t="n">
+      <c r="A4" s="2" t="n">
         <v>44256</v>
       </c>
       <c r="B4" t="n">
@@ -23780,7 +23926,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="3" t="n">
+      <c r="A5" s="2" t="n">
         <v>44287</v>
       </c>
       <c r="B5" t="n">
@@ -23806,7 +23952,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="3" t="n">
+      <c r="A6" s="2" t="n">
         <v>44317</v>
       </c>
       <c r="B6" t="n">
@@ -23832,7 +23978,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="3" t="n">
+      <c r="A7" s="2" t="n">
         <v>44348</v>
       </c>
       <c r="B7" t="n">
@@ -23858,7 +24004,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="3" t="n">
+      <c r="A8" s="2" t="n">
         <v>44378</v>
       </c>
       <c r="B8" t="n">
@@ -23884,7 +24030,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="3" t="n">
+      <c r="A9" s="2" t="n">
         <v>44409</v>
       </c>
       <c r="B9" t="n">
@@ -23910,7 +24056,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="3" t="n">
+      <c r="A10" s="2" t="n">
         <v>44440</v>
       </c>
       <c r="B10" t="n">
@@ -23936,7 +24082,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="3" t="n">
+      <c r="A11" s="2" t="n">
         <v>44470</v>
       </c>
       <c r="B11" t="n">
@@ -23962,7 +24108,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="3" t="n">
+      <c r="A12" s="2" t="n">
         <v>44501</v>
       </c>
       <c r="B12" t="n">
@@ -23988,7 +24134,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="3" t="n">
+      <c r="A13" s="2" t="n">
         <v>44531</v>
       </c>
       <c r="B13" t="n">
@@ -24014,7 +24160,7 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="3" t="n">
+      <c r="A14" s="2" t="n">
         <v>44562</v>
       </c>
       <c r="B14" t="n">
@@ -24040,7 +24186,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="3" t="n">
+      <c r="A15" s="2" t="n">
         <v>44593</v>
       </c>
       <c r="B15" t="n">
@@ -24066,7 +24212,7 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="3" t="n">
+      <c r="A16" s="2" t="n">
         <v>44621</v>
       </c>
       <c r="B16" t="n">
@@ -24092,7 +24238,7 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="3" t="n">
+      <c r="A17" s="2" t="n">
         <v>44652</v>
       </c>
       <c r="B17" t="n">
@@ -24118,7 +24264,7 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="3" t="n">
+      <c r="A18" s="2" t="n">
         <v>44682</v>
       </c>
       <c r="B18" t="n">
@@ -24144,7 +24290,7 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="3" t="n">
+      <c r="A19" s="2" t="n">
         <v>44713</v>
       </c>
       <c r="B19" t="n">
@@ -24170,7 +24316,7 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="3" t="n">
+      <c r="A20" s="2" t="n">
         <v>44743</v>
       </c>
       <c r="B20" t="n">
@@ -24196,7 +24342,7 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="3" t="n">
+      <c r="A21" s="2" t="n">
         <v>44774</v>
       </c>
       <c r="B21" t="n">
@@ -24222,7 +24368,7 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="3" t="n">
+      <c r="A22" s="2" t="n">
         <v>44805</v>
       </c>
       <c r="B22" t="n">
@@ -24248,7 +24394,7 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="3" t="n">
+      <c r="A23" s="2" t="n">
         <v>44835</v>
       </c>
       <c r="B23" t="n">
@@ -24274,7 +24420,7 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="3" t="n">
+      <c r="A24" s="2" t="n">
         <v>44866</v>
       </c>
       <c r="B24" t="n">
@@ -24300,7 +24446,7 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="3" t="n">
+      <c r="A25" s="2" t="n">
         <v>44896</v>
       </c>
       <c r="B25" t="n">
@@ -24326,7 +24472,7 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="3" t="n">
+      <c r="A26" s="2" t="n">
         <v>44927</v>
       </c>
       <c r="B26" t="n">
@@ -24352,7 +24498,7 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="3" t="n">
+      <c r="A27" s="2" t="n">
         <v>44958</v>
       </c>
       <c r="B27" t="n">
@@ -24378,7 +24524,7 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="3" t="n">
+      <c r="A28" s="2" t="n">
         <v>44986</v>
       </c>
       <c r="B28" t="n">
@@ -24404,7 +24550,7 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="3" t="n">
+      <c r="A29" s="2" t="n">
         <v>45017</v>
       </c>
       <c r="B29" t="n">
@@ -24430,7 +24576,7 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="3" t="n">
+      <c r="A30" s="2" t="n">
         <v>45047</v>
       </c>
       <c r="B30" t="n">
@@ -24456,7 +24602,7 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="3" t="n">
+      <c r="A31" s="2" t="n">
         <v>45078</v>
       </c>
       <c r="B31" t="n">
@@ -24482,7 +24628,7 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="3" t="n">
+      <c r="A32" s="2" t="n">
         <v>45108</v>
       </c>
       <c r="B32" t="n">
@@ -24508,7 +24654,7 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="3" t="n">
+      <c r="A33" s="2" t="n">
         <v>45139</v>
       </c>
       <c r="B33" t="n">
@@ -24534,7 +24680,7 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="3" t="n">
+      <c r="A34" s="2" t="n">
         <v>45170</v>
       </c>
       <c r="B34" t="n">
@@ -24560,7 +24706,7 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="3" t="n">
+      <c r="A35" s="2" t="n">
         <v>45200</v>
       </c>
       <c r="B35" t="n">
@@ -24586,7 +24732,7 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="3" t="n">
+      <c r="A36" s="2" t="n">
         <v>45231</v>
       </c>
       <c r="B36" t="n">
@@ -24612,7 +24758,7 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="3" t="n">
+      <c r="A37" s="2" t="n">
         <v>45261</v>
       </c>
       <c r="B37" t="n">
@@ -24638,7 +24784,7 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="3" t="n">
+      <c r="A38" s="2" t="n">
         <v>45292</v>
       </c>
       <c r="B38" t="n">
@@ -24664,7 +24810,7 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="3" t="n">
+      <c r="A39" s="2" t="n">
         <v>45323</v>
       </c>
       <c r="B39" t="n">
@@ -24690,7 +24836,7 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="3" t="n">
+      <c r="A40" s="2" t="n">
         <v>45352</v>
       </c>
       <c r="B40" t="n">
@@ -24716,7 +24862,7 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="3" t="n">
+      <c r="A41" s="2" t="n">
         <v>45383</v>
       </c>
       <c r="B41" t="n">
@@ -24742,7 +24888,7 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="3" t="n">
+      <c r="A42" s="2" t="n">
         <v>45413</v>
       </c>
       <c r="B42" t="n">
@@ -24768,7 +24914,7 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="3" t="n">
+      <c r="A43" s="2" t="n">
         <v>45444</v>
       </c>
       <c r="B43" t="n">
@@ -24794,7 +24940,7 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="3" t="n">
+      <c r="A44" s="2" t="n">
         <v>45474</v>
       </c>
       <c r="B44" t="n">
@@ -24820,7 +24966,7 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="3" t="n">
+      <c r="A45" s="2" t="n">
         <v>45505</v>
       </c>
       <c r="B45" t="n">
@@ -24846,7 +24992,7 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="3" t="n">
+      <c r="A46" s="2" t="n">
         <v>45536</v>
       </c>
       <c r="B46" t="n">
@@ -24872,7 +25018,7 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="3" t="n">
+      <c r="A47" s="2" t="n">
         <v>45566</v>
       </c>
       <c r="B47" t="n">
@@ -24898,7 +25044,7 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="3" t="n">
+      <c r="A48" s="2" t="n">
         <v>45597</v>
       </c>
       <c r="B48" t="n">
@@ -24924,7 +25070,7 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="3" t="n">
+      <c r="A49" s="2" t="n">
         <v>45627</v>
       </c>
       <c r="B49" t="n">
@@ -24950,7 +25096,7 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="3" t="n">
+      <c r="A50" s="2" t="n">
         <v>45658</v>
       </c>
       <c r="B50" t="n">
@@ -24976,7 +25122,7 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="3" t="n">
+      <c r="A51" s="2" t="n">
         <v>45689</v>
       </c>
       <c r="B51" t="n">
@@ -25002,7 +25148,7 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="3" t="n">
+      <c r="A52" s="2" t="n">
         <v>45717</v>
       </c>
       <c r="B52" t="n">
@@ -25028,7 +25174,7 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="3" t="n">
+      <c r="A53" s="2" t="n">
         <v>45748</v>
       </c>
       <c r="B53" t="n">
@@ -25054,7 +25200,7 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="3" t="n">
+      <c r="A54" s="2" t="n">
         <v>45778</v>
       </c>
       <c r="B54" t="n">
@@ -25080,7 +25226,7 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="3" t="n">
+      <c r="A55" s="2" t="n">
         <v>45809</v>
       </c>
       <c r="B55" t="n">
@@ -25106,7 +25252,7 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="3" t="n">
+      <c r="A56" s="2" t="n">
         <v>45839</v>
       </c>
       <c r="B56" t="n">
@@ -25132,7 +25278,7 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="3" t="n">
+      <c r="A57" s="2" t="n">
         <v>45870</v>
       </c>
       <c r="B57" t="n">
@@ -25158,7 +25304,7 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="3" t="n">
+      <c r="A58" s="2" t="n">
         <v>45901</v>
       </c>
       <c r="B58" t="n">
@@ -25184,7 +25330,7 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="3" t="n">
+      <c r="A59" s="2" t="n">
         <v>45931</v>
       </c>
       <c r="B59" t="n">
@@ -25210,7 +25356,7 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="3" t="n">
+      <c r="A60" s="2" t="n">
         <v>45962</v>
       </c>
       <c r="B60" t="n">
@@ -25236,7 +25382,7 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="3" t="n">
+      <c r="A61" s="2" t="n">
         <v>45992</v>
       </c>
       <c r="B61" t="n">
@@ -25262,7 +25408,7 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="3" t="n">
+      <c r="A62" s="2" t="n">
         <v>46023</v>
       </c>
       <c r="B62" t="n">
@@ -25288,7 +25434,7 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="3" t="n">
+      <c r="A63" s="2" t="n">
         <v>46054</v>
       </c>
       <c r="B63" t="n">
@@ -25314,7 +25460,7 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="3" t="n">
+      <c r="A64" s="2" t="n">
         <v>46082</v>
       </c>
       <c r="B64" t="n">
@@ -25340,7 +25486,7 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="3" t="n">
+      <c r="A65" s="2" t="n">
         <v>46113</v>
       </c>
       <c r="B65" t="n">
@@ -25366,7 +25512,7 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="3" t="n">
+      <c r="A66" s="2" t="n">
         <v>46143</v>
       </c>
       <c r="B66" t="n">
@@ -25452,7 +25598,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="3" t="n">
+      <c r="A2" s="2" t="n">
         <v>44197</v>
       </c>
       <c r="B2" t="n">
@@ -25478,7 +25624,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="n">
+      <c r="A3" s="2" t="n">
         <v>44228</v>
       </c>
       <c r="B3" t="n">
@@ -25504,7 +25650,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="3" t="n">
+      <c r="A4" s="2" t="n">
         <v>44256</v>
       </c>
       <c r="B4" t="n">
@@ -25530,7 +25676,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="3" t="n">
+      <c r="A5" s="2" t="n">
         <v>44287</v>
       </c>
       <c r="B5" t="n">
@@ -25556,7 +25702,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="3" t="n">
+      <c r="A6" s="2" t="n">
         <v>44317</v>
       </c>
       <c r="B6" t="n">
@@ -25582,7 +25728,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="3" t="n">
+      <c r="A7" s="2" t="n">
         <v>44348</v>
       </c>
       <c r="B7" t="n">
@@ -25608,7 +25754,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="3" t="n">
+      <c r="A8" s="2" t="n">
         <v>44378</v>
       </c>
       <c r="B8" t="n">
@@ -25634,7 +25780,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="3" t="n">
+      <c r="A9" s="2" t="n">
         <v>44409</v>
       </c>
       <c r="B9" t="n">
@@ -25660,7 +25806,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="3" t="n">
+      <c r="A10" s="2" t="n">
         <v>44440</v>
       </c>
       <c r="B10" t="n">
@@ -25686,7 +25832,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="3" t="n">
+      <c r="A11" s="2" t="n">
         <v>44470</v>
       </c>
       <c r="B11" t="n">
@@ -25712,7 +25858,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="3" t="n">
+      <c r="A12" s="2" t="n">
         <v>44501</v>
       </c>
       <c r="B12" t="n">
@@ -25738,7 +25884,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="3" t="n">
+      <c r="A13" s="2" t="n">
         <v>44531</v>
       </c>
       <c r="B13" t="n">
@@ -25764,7 +25910,7 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="3" t="n">
+      <c r="A14" s="2" t="n">
         <v>44562</v>
       </c>
       <c r="B14" t="n">
@@ -25790,7 +25936,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="3" t="n">
+      <c r="A15" s="2" t="n">
         <v>44593</v>
       </c>
       <c r="B15" t="n">
@@ -25816,7 +25962,7 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="3" t="n">
+      <c r="A16" s="2" t="n">
         <v>44621</v>
       </c>
       <c r="B16" t="n">
@@ -25842,7 +25988,7 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="3" t="n">
+      <c r="A17" s="2" t="n">
         <v>44652</v>
       </c>
       <c r="B17" t="n">
@@ -25868,7 +26014,7 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="3" t="n">
+      <c r="A18" s="2" t="n">
         <v>44682</v>
       </c>
       <c r="B18" t="n">
@@ -25894,7 +26040,7 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="3" t="n">
+      <c r="A19" s="2" t="n">
         <v>44713</v>
       </c>
       <c r="B19" t="n">
@@ -25920,7 +26066,7 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="3" t="n">
+      <c r="A20" s="2" t="n">
         <v>44743</v>
       </c>
       <c r="B20" t="n">
@@ -25946,7 +26092,7 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="3" t="n">
+      <c r="A21" s="2" t="n">
         <v>44774</v>
       </c>
       <c r="B21" t="n">
@@ -25972,7 +26118,7 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="3" t="n">
+      <c r="A22" s="2" t="n">
         <v>44805</v>
       </c>
       <c r="B22" t="n">
@@ -25998,7 +26144,7 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="3" t="n">
+      <c r="A23" s="2" t="n">
         <v>44835</v>
       </c>
       <c r="B23" t="n">
@@ -26024,7 +26170,7 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="3" t="n">
+      <c r="A24" s="2" t="n">
         <v>44866</v>
       </c>
       <c r="B24" t="n">
@@ -26050,7 +26196,7 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="3" t="n">
+      <c r="A25" s="2" t="n">
         <v>44896</v>
       </c>
       <c r="B25" t="n">
@@ -26076,7 +26222,7 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="3" t="n">
+      <c r="A26" s="2" t="n">
         <v>44927</v>
       </c>
       <c r="B26" t="n">
@@ -26102,7 +26248,7 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="3" t="n">
+      <c r="A27" s="2" t="n">
         <v>44958</v>
       </c>
       <c r="B27" t="n">
@@ -26128,7 +26274,7 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="3" t="n">
+      <c r="A28" s="2" t="n">
         <v>44986</v>
       </c>
       <c r="B28" t="n">
@@ -26154,7 +26300,7 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="3" t="n">
+      <c r="A29" s="2" t="n">
         <v>45017</v>
       </c>
       <c r="B29" t="n">
@@ -26180,7 +26326,7 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="3" t="n">
+      <c r="A30" s="2" t="n">
         <v>45047</v>
       </c>
       <c r="B30" t="n">
@@ -26206,7 +26352,7 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="3" t="n">
+      <c r="A31" s="2" t="n">
         <v>45078</v>
       </c>
       <c r="B31" t="n">
@@ -26232,7 +26378,7 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="3" t="n">
+      <c r="A32" s="2" t="n">
         <v>45108</v>
       </c>
       <c r="B32" t="n">
@@ -26258,7 +26404,7 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="3" t="n">
+      <c r="A33" s="2" t="n">
         <v>45139</v>
       </c>
       <c r="B33" t="n">
@@ -26284,7 +26430,7 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="3" t="n">
+      <c r="A34" s="2" t="n">
         <v>45170</v>
       </c>
       <c r="B34" t="n">
@@ -26310,7 +26456,7 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="3" t="n">
+      <c r="A35" s="2" t="n">
         <v>45200</v>
       </c>
       <c r="B35" t="n">
@@ -26336,7 +26482,7 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="3" t="n">
+      <c r="A36" s="2" t="n">
         <v>45231</v>
       </c>
       <c r="B36" t="n">
@@ -26362,7 +26508,7 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="3" t="n">
+      <c r="A37" s="2" t="n">
         <v>45261</v>
       </c>
       <c r="B37" t="n">
@@ -26388,7 +26534,7 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="3" t="n">
+      <c r="A38" s="2" t="n">
         <v>45292</v>
       </c>
       <c r="B38" t="n">
@@ -26414,7 +26560,7 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="3" t="n">
+      <c r="A39" s="2" t="n">
         <v>45323</v>
       </c>
       <c r="B39" t="n">
@@ -26440,7 +26586,7 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="3" t="n">
+      <c r="A40" s="2" t="n">
         <v>45352</v>
       </c>
       <c r="B40" t="n">
@@ -26466,7 +26612,7 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="3" t="n">
+      <c r="A41" s="2" t="n">
         <v>45383</v>
       </c>
       <c r="B41" t="n">
@@ -26492,7 +26638,7 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="3" t="n">
+      <c r="A42" s="2" t="n">
         <v>45413</v>
       </c>
       <c r="B42" t="n">
@@ -26518,7 +26664,7 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="3" t="n">
+      <c r="A43" s="2" t="n">
         <v>45444</v>
       </c>
       <c r="B43" t="n">
@@ -26544,7 +26690,7 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="3" t="n">
+      <c r="A44" s="2" t="n">
         <v>45474</v>
       </c>
       <c r="B44" t="n">
@@ -26570,7 +26716,7 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="3" t="n">
+      <c r="A45" s="2" t="n">
         <v>45505</v>
       </c>
       <c r="B45" t="n">
@@ -26596,7 +26742,7 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="3" t="n">
+      <c r="A46" s="2" t="n">
         <v>45536</v>
       </c>
       <c r="B46" t="n">
@@ -26622,7 +26768,7 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="3" t="n">
+      <c r="A47" s="2" t="n">
         <v>45566</v>
       </c>
       <c r="B47" t="n">
@@ -26648,7 +26794,7 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="3" t="n">
+      <c r="A48" s="2" t="n">
         <v>45597</v>
       </c>
       <c r="B48" t="n">
@@ -26674,7 +26820,7 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="3" t="n">
+      <c r="A49" s="2" t="n">
         <v>45627</v>
       </c>
       <c r="B49" t="n">
@@ -26700,7 +26846,7 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="3" t="n">
+      <c r="A50" s="2" t="n">
         <v>45658</v>
       </c>
       <c r="B50" t="n">
@@ -26726,7 +26872,7 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="3" t="n">
+      <c r="A51" s="2" t="n">
         <v>45689</v>
       </c>
       <c r="B51" t="n">
@@ -26752,7 +26898,7 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="3" t="n">
+      <c r="A52" s="2" t="n">
         <v>45717</v>
       </c>
       <c r="B52" t="n">
@@ -26778,7 +26924,7 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="3" t="n">
+      <c r="A53" s="2" t="n">
         <v>45748</v>
       </c>
       <c r="B53" t="n">
@@ -26804,7 +26950,7 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="3" t="n">
+      <c r="A54" s="2" t="n">
         <v>45778</v>
       </c>
       <c r="B54" t="n">
@@ -26830,7 +26976,7 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="3" t="n">
+      <c r="A55" s="2" t="n">
         <v>45809</v>
       </c>
       <c r="B55" t="n">
@@ -26856,7 +27002,7 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="3" t="n">
+      <c r="A56" s="2" t="n">
         <v>45839</v>
       </c>
       <c r="B56" t="n">
@@ -26882,7 +27028,7 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="3" t="n">
+      <c r="A57" s="2" t="n">
         <v>45870</v>
       </c>
       <c r="B57" t="n">
@@ -26908,7 +27054,7 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="3" t="n">
+      <c r="A58" s="2" t="n">
         <v>45901</v>
       </c>
       <c r="B58" t="n">
@@ -26934,7 +27080,7 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="3" t="n">
+      <c r="A59" s="2" t="n">
         <v>45931</v>
       </c>
       <c r="B59" t="n">
@@ -26960,7 +27106,7 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="3" t="n">
+      <c r="A60" s="2" t="n">
         <v>45962</v>
       </c>
       <c r="B60" t="n">
@@ -26986,7 +27132,7 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="3" t="n">
+      <c r="A61" s="2" t="n">
         <v>45992</v>
       </c>
       <c r="B61" t="n">
@@ -27012,7 +27158,7 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="3" t="n">
+      <c r="A62" s="2" t="n">
         <v>46023</v>
       </c>
       <c r="B62" t="n">
@@ -27038,7 +27184,7 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="3" t="n">
+      <c r="A63" s="2" t="n">
         <v>46054</v>
       </c>
       <c r="B63" t="n">
@@ -27064,7 +27210,7 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="3" t="n">
+      <c r="A64" s="2" t="n">
         <v>46082</v>
       </c>
       <c r="B64" t="n">
@@ -27090,7 +27236,7 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="3" t="n">
+      <c r="A65" s="2" t="n">
         <v>46113</v>
       </c>
       <c r="B65" t="n">
@@ -27176,7 +27322,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="3" t="n">
+      <c r="A2" s="2" t="n">
         <v>44197</v>
       </c>
       <c r="B2" t="n">
@@ -27202,7 +27348,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="n">
+      <c r="A3" s="2" t="n">
         <v>44228</v>
       </c>
       <c r="B3" t="n">
@@ -27228,7 +27374,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="3" t="n">
+      <c r="A4" s="2" t="n">
         <v>44256</v>
       </c>
       <c r="B4" t="n">
@@ -27254,7 +27400,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="3" t="n">
+      <c r="A5" s="2" t="n">
         <v>44287</v>
       </c>
       <c r="B5" t="n">
@@ -27280,7 +27426,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="3" t="n">
+      <c r="A6" s="2" t="n">
         <v>44317</v>
       </c>
       <c r="B6" t="n">
@@ -27306,7 +27452,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="3" t="n">
+      <c r="A7" s="2" t="n">
         <v>44348</v>
       </c>
       <c r="B7" t="n">
@@ -27332,7 +27478,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="3" t="n">
+      <c r="A8" s="2" t="n">
         <v>44378</v>
       </c>
       <c r="B8" t="n">
@@ -27358,7 +27504,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="3" t="n">
+      <c r="A9" s="2" t="n">
         <v>44409</v>
       </c>
       <c r="B9" t="n">
@@ -27384,7 +27530,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="3" t="n">
+      <c r="A10" s="2" t="n">
         <v>44440</v>
       </c>
       <c r="B10" t="n">
@@ -27410,7 +27556,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="3" t="n">
+      <c r="A11" s="2" t="n">
         <v>44470</v>
       </c>
       <c r="B11" t="n">
@@ -27436,7 +27582,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="3" t="n">
+      <c r="A12" s="2" t="n">
         <v>44501</v>
       </c>
       <c r="B12" t="n">
@@ -27462,7 +27608,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="3" t="n">
+      <c r="A13" s="2" t="n">
         <v>44531</v>
       </c>
       <c r="B13" t="n">
@@ -27488,7 +27634,7 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="3" t="n">
+      <c r="A14" s="2" t="n">
         <v>44562</v>
       </c>
       <c r="B14" t="n">
@@ -27514,7 +27660,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="3" t="n">
+      <c r="A15" s="2" t="n">
         <v>44593</v>
       </c>
       <c r="B15" t="n">
@@ -27540,7 +27686,7 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="3" t="n">
+      <c r="A16" s="2" t="n">
         <v>44621</v>
       </c>
       <c r="B16" t="n">
@@ -27566,7 +27712,7 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="3" t="n">
+      <c r="A17" s="2" t="n">
         <v>44652</v>
       </c>
       <c r="B17" t="n">
@@ -27592,7 +27738,7 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="3" t="n">
+      <c r="A18" s="2" t="n">
         <v>44682</v>
       </c>
       <c r="B18" t="n">
@@ -27618,7 +27764,7 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="3" t="n">
+      <c r="A19" s="2" t="n">
         <v>44713</v>
       </c>
       <c r="B19" t="n">
@@ -27644,7 +27790,7 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="3" t="n">
+      <c r="A20" s="2" t="n">
         <v>44743</v>
       </c>
       <c r="B20" t="n">
@@ -27670,7 +27816,7 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="3" t="n">
+      <c r="A21" s="2" t="n">
         <v>44774</v>
       </c>
       <c r="B21" t="n">
@@ -27696,7 +27842,7 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="3" t="n">
+      <c r="A22" s="2" t="n">
         <v>44805</v>
       </c>
       <c r="B22" t="n">
@@ -27722,7 +27868,7 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="3" t="n">
+      <c r="A23" s="2" t="n">
         <v>44835</v>
       </c>
       <c r="B23" t="n">
@@ -27748,7 +27894,7 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="3" t="n">
+      <c r="A24" s="2" t="n">
         <v>44866</v>
       </c>
       <c r="B24" t="n">
@@ -27774,7 +27920,7 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="3" t="n">
+      <c r="A25" s="2" t="n">
         <v>44896</v>
       </c>
       <c r="B25" t="n">
@@ -27800,7 +27946,7 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="3" t="n">
+      <c r="A26" s="2" t="n">
         <v>44927</v>
       </c>
       <c r="B26" t="n">
@@ -27826,7 +27972,7 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="3" t="n">
+      <c r="A27" s="2" t="n">
         <v>44958</v>
       </c>
       <c r="B27" t="n">
@@ -27852,7 +27998,7 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="3" t="n">
+      <c r="A28" s="2" t="n">
         <v>44986</v>
       </c>
       <c r="B28" t="n">
@@ -27878,7 +28024,7 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="3" t="n">
+      <c r="A29" s="2" t="n">
         <v>45017</v>
       </c>
       <c r="B29" t="n">
@@ -27904,7 +28050,7 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="3" t="n">
+      <c r="A30" s="2" t="n">
         <v>45047</v>
       </c>
       <c r="B30" t="n">
@@ -27930,7 +28076,7 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="3" t="n">
+      <c r="A31" s="2" t="n">
         <v>45078</v>
       </c>
       <c r="B31" t="n">
@@ -27956,7 +28102,7 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="3" t="n">
+      <c r="A32" s="2" t="n">
         <v>45108</v>
       </c>
       <c r="B32" t="n">
@@ -27982,7 +28128,7 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="3" t="n">
+      <c r="A33" s="2" t="n">
         <v>45139</v>
       </c>
       <c r="B33" t="n">
@@ -28008,7 +28154,7 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="3" t="n">
+      <c r="A34" s="2" t="n">
         <v>45170</v>
       </c>
       <c r="B34" t="n">
@@ -28034,7 +28180,7 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="3" t="n">
+      <c r="A35" s="2" t="n">
         <v>45200</v>
       </c>
       <c r="B35" t="n">
@@ -28060,7 +28206,7 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="3" t="n">
+      <c r="A36" s="2" t="n">
         <v>45231</v>
       </c>
       <c r="B36" t="n">
@@ -28086,7 +28232,7 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="3" t="n">
+      <c r="A37" s="2" t="n">
         <v>45261</v>
       </c>
       <c r="B37" t="n">
@@ -28112,7 +28258,7 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="3" t="n">
+      <c r="A38" s="2" t="n">
         <v>45292</v>
       </c>
       <c r="B38" t="n">
@@ -28138,7 +28284,7 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="3" t="n">
+      <c r="A39" s="2" t="n">
         <v>45323</v>
       </c>
       <c r="B39" t="n">
@@ -28164,7 +28310,7 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="3" t="n">
+      <c r="A40" s="2" t="n">
         <v>45352</v>
       </c>
       <c r="B40" t="n">
@@ -28190,7 +28336,7 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="3" t="n">
+      <c r="A41" s="2" t="n">
         <v>45383</v>
       </c>
       <c r="B41" t="n">
@@ -28216,7 +28362,7 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="3" t="n">
+      <c r="A42" s="2" t="n">
         <v>45413</v>
       </c>
       <c r="B42" t="n">
@@ -28242,7 +28388,7 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="3" t="n">
+      <c r="A43" s="2" t="n">
         <v>45444</v>
       </c>
       <c r="B43" t="n">
@@ -28268,7 +28414,7 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="3" t="n">
+      <c r="A44" s="2" t="n">
         <v>45474</v>
       </c>
       <c r="B44" t="n">
@@ -28294,7 +28440,7 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="3" t="n">
+      <c r="A45" s="2" t="n">
         <v>45505</v>
       </c>
       <c r="B45" t="n">
@@ -28320,7 +28466,7 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="3" t="n">
+      <c r="A46" s="2" t="n">
         <v>45536</v>
       </c>
       <c r="B46" t="n">
@@ -28346,7 +28492,7 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="3" t="n">
+      <c r="A47" s="2" t="n">
         <v>45566</v>
       </c>
       <c r="B47" t="n">
@@ -28372,7 +28518,7 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="3" t="n">
+      <c r="A48" s="2" t="n">
         <v>45597</v>
       </c>
       <c r="B48" t="n">
@@ -28398,7 +28544,7 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="3" t="n">
+      <c r="A49" s="2" t="n">
         <v>45627</v>
       </c>
       <c r="B49" t="n">
@@ -28424,7 +28570,7 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="3" t="n">
+      <c r="A50" s="2" t="n">
         <v>45658</v>
       </c>
       <c r="B50" t="n">
@@ -28450,7 +28596,7 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="3" t="n">
+      <c r="A51" s="2" t="n">
         <v>45689</v>
       </c>
       <c r="B51" t="n">
@@ -28476,7 +28622,7 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="3" t="n">
+      <c r="A52" s="2" t="n">
         <v>45717</v>
       </c>
       <c r="B52" t="n">
@@ -28502,7 +28648,7 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="3" t="n">
+      <c r="A53" s="2" t="n">
         <v>45748</v>
       </c>
       <c r="B53" t="n">
@@ -28528,7 +28674,7 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="3" t="n">
+      <c r="A54" s="2" t="n">
         <v>45778</v>
       </c>
       <c r="B54" t="n">
@@ -28554,7 +28700,7 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="3" t="n">
+      <c r="A55" s="2" t="n">
         <v>45809</v>
       </c>
       <c r="B55" t="n">
@@ -28580,7 +28726,7 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="3" t="n">
+      <c r="A56" s="2" t="n">
         <v>45839</v>
       </c>
       <c r="B56" t="n">
@@ -28606,7 +28752,7 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="3" t="n">
+      <c r="A57" s="2" t="n">
         <v>45870</v>
       </c>
       <c r="B57" t="n">
@@ -28632,7 +28778,7 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="3" t="n">
+      <c r="A58" s="2" t="n">
         <v>45901</v>
       </c>
       <c r="B58" t="n">
@@ -28658,7 +28804,7 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="3" t="n">
+      <c r="A59" s="2" t="n">
         <v>45931</v>
       </c>
       <c r="B59" t="n">
@@ -28684,7 +28830,7 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="3" t="n">
+      <c r="A60" s="2" t="n">
         <v>45962</v>
       </c>
       <c r="B60" t="n">
@@ -28710,7 +28856,7 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="3" t="n">
+      <c r="A61" s="2" t="n">
         <v>45992</v>
       </c>
       <c r="B61" t="n">
@@ -28736,7 +28882,7 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="3" t="n">
+      <c r="A62" s="2" t="n">
         <v>46023</v>
       </c>
       <c r="B62" t="n">
@@ -28762,7 +28908,7 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="3" t="n">
+      <c r="A63" s="2" t="n">
         <v>46054</v>
       </c>
       <c r="B63" t="n">
@@ -28788,7 +28934,7 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="3" t="n">
+      <c r="A64" s="2" t="n">
         <v>46082</v>
       </c>
       <c r="B64" t="n">
@@ -28814,7 +28960,7 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="3" t="n">
+      <c r="A65" s="2" t="n">
         <v>46113</v>
       </c>
       <c r="B65" t="n">
@@ -28900,7 +29046,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="3" t="n">
+      <c r="A2" s="2" t="n">
         <v>44197</v>
       </c>
       <c r="B2" t="n">
@@ -28926,7 +29072,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="n">
+      <c r="A3" s="2" t="n">
         <v>44228</v>
       </c>
       <c r="B3" t="n">
@@ -28952,7 +29098,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="3" t="n">
+      <c r="A4" s="2" t="n">
         <v>44256</v>
       </c>
       <c r="B4" t="n">
@@ -28978,7 +29124,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="3" t="n">
+      <c r="A5" s="2" t="n">
         <v>44287</v>
       </c>
       <c r="B5" t="n">
@@ -29004,7 +29150,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="3" t="n">
+      <c r="A6" s="2" t="n">
         <v>44317</v>
       </c>
       <c r="B6" t="n">
@@ -29030,7 +29176,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="3" t="n">
+      <c r="A7" s="2" t="n">
         <v>44348</v>
       </c>
       <c r="B7" t="n">
@@ -29056,7 +29202,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="3" t="n">
+      <c r="A8" s="2" t="n">
         <v>44378</v>
       </c>
       <c r="B8" t="n">
@@ -29082,7 +29228,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="3" t="n">
+      <c r="A9" s="2" t="n">
         <v>44409</v>
       </c>
       <c r="B9" t="n">
@@ -29108,7 +29254,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="3" t="n">
+      <c r="A10" s="2" t="n">
         <v>44440</v>
       </c>
       <c r="B10" t="n">
@@ -29134,7 +29280,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="3" t="n">
+      <c r="A11" s="2" t="n">
         <v>44470</v>
       </c>
       <c r="B11" t="n">
@@ -29160,7 +29306,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="3" t="n">
+      <c r="A12" s="2" t="n">
         <v>44501</v>
       </c>
       <c r="B12" t="n">
@@ -29186,7 +29332,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="3" t="n">
+      <c r="A13" s="2" t="n">
         <v>44531</v>
       </c>
       <c r="B13" t="n">
@@ -29212,7 +29358,7 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="3" t="n">
+      <c r="A14" s="2" t="n">
         <v>44562</v>
       </c>
       <c r="B14" t="n">
@@ -29238,7 +29384,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="3" t="n">
+      <c r="A15" s="2" t="n">
         <v>44593</v>
       </c>
       <c r="B15" t="n">
@@ -29264,7 +29410,7 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="3" t="n">
+      <c r="A16" s="2" t="n">
         <v>44621</v>
       </c>
       <c r="B16" t="n">
@@ -29290,7 +29436,7 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="3" t="n">
+      <c r="A17" s="2" t="n">
         <v>44652</v>
       </c>
       <c r="B17" t="n">
@@ -29316,7 +29462,7 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="3" t="n">
+      <c r="A18" s="2" t="n">
         <v>44682</v>
       </c>
       <c r="B18" t="n">
@@ -29342,7 +29488,7 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="3" t="n">
+      <c r="A19" s="2" t="n">
         <v>44713</v>
       </c>
       <c r="B19" t="n">
@@ -29368,7 +29514,7 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="3" t="n">
+      <c r="A20" s="2" t="n">
         <v>44743</v>
       </c>
       <c r="B20" t="n">
@@ -29394,7 +29540,7 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="3" t="n">
+      <c r="A21" s="2" t="n">
         <v>44774</v>
       </c>
       <c r="B21" t="n">
@@ -29420,7 +29566,7 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="3" t="n">
+      <c r="A22" s="2" t="n">
         <v>44805</v>
       </c>
       <c r="B22" t="n">
@@ -29446,7 +29592,7 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="3" t="n">
+      <c r="A23" s="2" t="n">
         <v>44835</v>
       </c>
       <c r="B23" t="n">
@@ -29472,7 +29618,7 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="3" t="n">
+      <c r="A24" s="2" t="n">
         <v>44866</v>
       </c>
       <c r="B24" t="n">
@@ -29498,7 +29644,7 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="3" t="n">
+      <c r="A25" s="2" t="n">
         <v>44896</v>
       </c>
       <c r="B25" t="n">
@@ -29524,7 +29670,7 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="3" t="n">
+      <c r="A26" s="2" t="n">
         <v>44927</v>
       </c>
       <c r="B26" t="n">
@@ -29550,7 +29696,7 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="3" t="n">
+      <c r="A27" s="2" t="n">
         <v>44958</v>
       </c>
       <c r="B27" t="n">
@@ -29576,7 +29722,7 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="3" t="n">
+      <c r="A28" s="2" t="n">
         <v>44986</v>
       </c>
       <c r="B28" t="n">
@@ -29602,7 +29748,7 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="3" t="n">
+      <c r="A29" s="2" t="n">
         <v>45017</v>
       </c>
       <c r="B29" t="n">
@@ -29628,7 +29774,7 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="3" t="n">
+      <c r="A30" s="2" t="n">
         <v>45047</v>
       </c>
       <c r="B30" t="n">
@@ -29654,7 +29800,7 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="3" t="n">
+      <c r="A31" s="2" t="n">
         <v>45078</v>
       </c>
       <c r="B31" t="n">
@@ -29680,7 +29826,7 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="3" t="n">
+      <c r="A32" s="2" t="n">
         <v>45108</v>
       </c>
       <c r="B32" t="n">
@@ -29706,7 +29852,7 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="3" t="n">
+      <c r="A33" s="2" t="n">
         <v>45139</v>
       </c>
       <c r="B33" t="n">
@@ -29732,7 +29878,7 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="3" t="n">
+      <c r="A34" s="2" t="n">
         <v>45170</v>
       </c>
       <c r="B34" t="n">
@@ -29758,7 +29904,7 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="3" t="n">
+      <c r="A35" s="2" t="n">
         <v>45200</v>
       </c>
       <c r="B35" t="n">
@@ -29784,7 +29930,7 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="3" t="n">
+      <c r="A36" s="2" t="n">
         <v>45231</v>
       </c>
       <c r="B36" t="n">
@@ -29810,7 +29956,7 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="3" t="n">
+      <c r="A37" s="2" t="n">
         <v>45261</v>
       </c>
       <c r="B37" t="n">
@@ -29836,7 +29982,7 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="3" t="n">
+      <c r="A38" s="2" t="n">
         <v>45292</v>
       </c>
       <c r="B38" t="n">
@@ -29862,7 +30008,7 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="3" t="n">
+      <c r="A39" s="2" t="n">
         <v>45323</v>
       </c>
       <c r="B39" t="n">
@@ -29888,7 +30034,7 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="3" t="n">
+      <c r="A40" s="2" t="n">
         <v>45352</v>
       </c>
       <c r="B40" t="n">
@@ -29914,7 +30060,7 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="3" t="n">
+      <c r="A41" s="2" t="n">
         <v>45383</v>
       </c>
       <c r="B41" t="n">
@@ -29940,7 +30086,7 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="3" t="n">
+      <c r="A42" s="2" t="n">
         <v>45413</v>
       </c>
       <c r="B42" t="n">
@@ -29966,7 +30112,7 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="3" t="n">
+      <c r="A43" s="2" t="n">
         <v>45444</v>
       </c>
       <c r="B43" t="n">
@@ -29992,7 +30138,7 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="3" t="n">
+      <c r="A44" s="2" t="n">
         <v>45474</v>
       </c>
       <c r="B44" t="n">
@@ -30018,7 +30164,7 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="3" t="n">
+      <c r="A45" s="2" t="n">
         <v>45505</v>
       </c>
       <c r="B45" t="n">
@@ -30044,7 +30190,7 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="3" t="n">
+      <c r="A46" s="2" t="n">
         <v>45536</v>
       </c>
       <c r="B46" t="n">
@@ -30070,7 +30216,7 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="3" t="n">
+      <c r="A47" s="2" t="n">
         <v>45566</v>
       </c>
       <c r="B47" t="n">
@@ -30096,7 +30242,7 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="3" t="n">
+      <c r="A48" s="2" t="n">
         <v>45597</v>
       </c>
       <c r="B48" t="n">
@@ -30122,7 +30268,7 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="3" t="n">
+      <c r="A49" s="2" t="n">
         <v>45627</v>
       </c>
       <c r="B49" t="n">
@@ -30148,7 +30294,7 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="3" t="n">
+      <c r="A50" s="2" t="n">
         <v>45658</v>
       </c>
       <c r="B50" t="n">
@@ -30174,7 +30320,7 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="3" t="n">
+      <c r="A51" s="2" t="n">
         <v>45689</v>
       </c>
       <c r="B51" t="n">
@@ -30200,7 +30346,7 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="3" t="n">
+      <c r="A52" s="2" t="n">
         <v>45717</v>
       </c>
       <c r="B52" t="n">
@@ -30226,7 +30372,7 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="3" t="n">
+      <c r="A53" s="2" t="n">
         <v>45748</v>
       </c>
       <c r="B53" t="n">
@@ -30252,7 +30398,7 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="3" t="n">
+      <c r="A54" s="2" t="n">
         <v>45778</v>
       </c>
       <c r="B54" t="n">
@@ -30278,7 +30424,7 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="3" t="n">
+      <c r="A55" s="2" t="n">
         <v>45809</v>
       </c>
       <c r="B55" t="n">
@@ -30304,7 +30450,7 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="3" t="n">
+      <c r="A56" s="2" t="n">
         <v>45839</v>
       </c>
       <c r="B56" t="n">
@@ -30330,7 +30476,7 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="3" t="n">
+      <c r="A57" s="2" t="n">
         <v>45870</v>
       </c>
       <c r="B57" t="n">
@@ -30356,7 +30502,7 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="3" t="n">
+      <c r="A58" s="2" t="n">
         <v>45901</v>
       </c>
       <c r="B58" t="n">
@@ -30382,7 +30528,7 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="3" t="n">
+      <c r="A59" s="2" t="n">
         <v>45931</v>
       </c>
       <c r="B59" t="n">
@@ -30408,7 +30554,7 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="3" t="n">
+      <c r="A60" s="2" t="n">
         <v>45962</v>
       </c>
       <c r="B60" t="n">
@@ -30434,7 +30580,7 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="3" t="n">
+      <c r="A61" s="2" t="n">
         <v>45992</v>
       </c>
       <c r="B61" t="n">
@@ -30520,7 +30666,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="3" t="n">
+      <c r="A2" s="2" t="n">
         <v>44197</v>
       </c>
       <c r="B2" t="n">
@@ -30546,7 +30692,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="n">
+      <c r="A3" s="2" t="n">
         <v>44228</v>
       </c>
       <c r="B3" t="n">
@@ -30572,7 +30718,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="3" t="n">
+      <c r="A4" s="2" t="n">
         <v>44256</v>
       </c>
       <c r="B4" t="n">
@@ -30598,7 +30744,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="3" t="n">
+      <c r="A5" s="2" t="n">
         <v>44287</v>
       </c>
       <c r="B5" t="n">
@@ -30624,7 +30770,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="3" t="n">
+      <c r="A6" s="2" t="n">
         <v>44317</v>
       </c>
       <c r="B6" t="n">
@@ -30650,7 +30796,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="3" t="n">
+      <c r="A7" s="2" t="n">
         <v>44348</v>
       </c>
       <c r="B7" t="n">
@@ -30676,7 +30822,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="3" t="n">
+      <c r="A8" s="2" t="n">
         <v>44378</v>
       </c>
       <c r="B8" t="n">
@@ -30702,7 +30848,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="3" t="n">
+      <c r="A9" s="2" t="n">
         <v>44409</v>
       </c>
       <c r="B9" t="n">
@@ -30728,7 +30874,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="3" t="n">
+      <c r="A10" s="2" t="n">
         <v>44440</v>
       </c>
       <c r="B10" t="n">
@@ -30754,7 +30900,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="3" t="n">
+      <c r="A11" s="2" t="n">
         <v>44470</v>
       </c>
       <c r="B11" t="n">
@@ -30780,7 +30926,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="3" t="n">
+      <c r="A12" s="2" t="n">
         <v>44501</v>
       </c>
       <c r="B12" t="n">
@@ -30806,7 +30952,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="3" t="n">
+      <c r="A13" s="2" t="n">
         <v>44531</v>
       </c>
       <c r="B13" t="n">
@@ -30832,7 +30978,7 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="3" t="n">
+      <c r="A14" s="2" t="n">
         <v>44562</v>
       </c>
       <c r="B14" t="n">
@@ -30858,7 +31004,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="3" t="n">
+      <c r="A15" s="2" t="n">
         <v>44593</v>
       </c>
       <c r="B15" t="n">
@@ -30884,7 +31030,7 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="3" t="n">
+      <c r="A16" s="2" t="n">
         <v>44621</v>
       </c>
       <c r="B16" t="n">
@@ -30910,7 +31056,7 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="3" t="n">
+      <c r="A17" s="2" t="n">
         <v>44652</v>
       </c>
       <c r="B17" t="n">
@@ -30936,7 +31082,7 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="3" t="n">
+      <c r="A18" s="2" t="n">
         <v>44682</v>
       </c>
       <c r="B18" t="n">
@@ -30962,7 +31108,7 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="3" t="n">
+      <c r="A19" s="2" t="n">
         <v>44713</v>
       </c>
       <c r="B19" t="n">
@@ -30988,7 +31134,7 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="3" t="n">
+      <c r="A20" s="2" t="n">
         <v>44743</v>
       </c>
       <c r="B20" t="n">
@@ -31014,7 +31160,7 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="3" t="n">
+      <c r="A21" s="2" t="n">
         <v>44774</v>
       </c>
       <c r="B21" t="n">
@@ -31040,7 +31186,7 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="3" t="n">
+      <c r="A22" s="2" t="n">
         <v>44805</v>
       </c>
       <c r="B22" t="n">
@@ -31066,7 +31212,7 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="3" t="n">
+      <c r="A23" s="2" t="n">
         <v>44835</v>
       </c>
       <c r="B23" t="n">
@@ -31092,7 +31238,7 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="3" t="n">
+      <c r="A24" s="2" t="n">
         <v>44866</v>
       </c>
       <c r="B24" t="n">
@@ -31118,7 +31264,7 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="3" t="n">
+      <c r="A25" s="2" t="n">
         <v>44896</v>
       </c>
       <c r="B25" t="n">
@@ -31144,7 +31290,7 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="3" t="n">
+      <c r="A26" s="2" t="n">
         <v>44927</v>
       </c>
       <c r="B26" t="n">
@@ -31170,7 +31316,7 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="3" t="n">
+      <c r="A27" s="2" t="n">
         <v>44958</v>
       </c>
       <c r="B27" t="n">
@@ -31196,7 +31342,7 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="3" t="n">
+      <c r="A28" s="2" t="n">
         <v>44986</v>
       </c>
       <c r="B28" t="n">
@@ -31222,7 +31368,7 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="3" t="n">
+      <c r="A29" s="2" t="n">
         <v>45017</v>
       </c>
       <c r="B29" t="n">
@@ -31248,7 +31394,7 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="3" t="n">
+      <c r="A30" s="2" t="n">
         <v>45047</v>
       </c>
       <c r="B30" t="n">
@@ -31274,7 +31420,7 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="3" t="n">
+      <c r="A31" s="2" t="n">
         <v>45078</v>
       </c>
       <c r="B31" t="n">
@@ -31300,7 +31446,7 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="3" t="n">
+      <c r="A32" s="2" t="n">
         <v>45108</v>
       </c>
       <c r="B32" t="n">
@@ -31326,7 +31472,7 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="3" t="n">
+      <c r="A33" s="2" t="n">
         <v>45139</v>
       </c>
       <c r="B33" t="n">
@@ -31352,7 +31498,7 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="3" t="n">
+      <c r="A34" s="2" t="n">
         <v>45170</v>
       </c>
       <c r="B34" t="n">
@@ -31378,7 +31524,7 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="3" t="n">
+      <c r="A35" s="2" t="n">
         <v>45200</v>
       </c>
       <c r="B35" t="n">
@@ -31404,7 +31550,7 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="3" t="n">
+      <c r="A36" s="2" t="n">
         <v>45231</v>
       </c>
       <c r="B36" t="n">
@@ -31430,7 +31576,7 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="3" t="n">
+      <c r="A37" s="2" t="n">
         <v>45261</v>
       </c>
       <c r="B37" t="n">
@@ -31456,7 +31602,7 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="3" t="n">
+      <c r="A38" s="2" t="n">
         <v>45292</v>
       </c>
       <c r="B38" t="n">
@@ -31482,7 +31628,7 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="3" t="n">
+      <c r="A39" s="2" t="n">
         <v>45323</v>
       </c>
       <c r="B39" t="n">
@@ -31508,7 +31654,7 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="3" t="n">
+      <c r="A40" s="2" t="n">
         <v>45352</v>
       </c>
       <c r="B40" t="n">
@@ -31534,7 +31680,7 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="3" t="n">
+      <c r="A41" s="2" t="n">
         <v>45383</v>
       </c>
       <c r="B41" t="n">
@@ -31560,7 +31706,7 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="3" t="n">
+      <c r="A42" s="2" t="n">
         <v>45413</v>
       </c>
       <c r="B42" t="n">
@@ -31586,7 +31732,7 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="3" t="n">
+      <c r="A43" s="2" t="n">
         <v>45444</v>
       </c>
       <c r="B43" t="n">
@@ -31612,7 +31758,7 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="3" t="n">
+      <c r="A44" s="2" t="n">
         <v>45474</v>
       </c>
       <c r="B44" t="n">
@@ -31638,7 +31784,7 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="3" t="n">
+      <c r="A45" s="2" t="n">
         <v>45505</v>
       </c>
       <c r="B45" t="n">
@@ -31664,7 +31810,7 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="3" t="n">
+      <c r="A46" s="2" t="n">
         <v>45536</v>
       </c>
       <c r="B46" t="n">
@@ -31690,7 +31836,7 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="3" t="n">
+      <c r="A47" s="2" t="n">
         <v>45566</v>
       </c>
       <c r="B47" t="n">
@@ -31716,7 +31862,7 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="3" t="n">
+      <c r="A48" s="2" t="n">
         <v>45597</v>
       </c>
       <c r="B48" t="n">
@@ -31742,7 +31888,7 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="3" t="n">
+      <c r="A49" s="2" t="n">
         <v>45627</v>
       </c>
       <c r="B49" t="n">
@@ -31768,7 +31914,7 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="3" t="n">
+      <c r="A50" s="2" t="n">
         <v>45658</v>
       </c>
       <c r="B50" t="n">
@@ -31794,7 +31940,7 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="3" t="n">
+      <c r="A51" s="2" t="n">
         <v>45689</v>
       </c>
       <c r="B51" t="n">
@@ -31820,7 +31966,7 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="3" t="n">
+      <c r="A52" s="2" t="n">
         <v>45717</v>
       </c>
       <c r="B52" t="n">
@@ -31846,7 +31992,7 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="3" t="n">
+      <c r="A53" s="2" t="n">
         <v>45748</v>
       </c>
       <c r="B53" t="n">
@@ -31872,7 +32018,7 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="3" t="n">
+      <c r="A54" s="2" t="n">
         <v>45778</v>
       </c>
       <c r="B54" t="n">
@@ -31898,7 +32044,7 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="3" t="n">
+      <c r="A55" s="2" t="n">
         <v>45809</v>
       </c>
       <c r="B55" t="n">
@@ -31924,7 +32070,7 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="3" t="n">
+      <c r="A56" s="2" t="n">
         <v>45839</v>
       </c>
       <c r="B56" t="n">
@@ -31950,7 +32096,7 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="3" t="n">
+      <c r="A57" s="2" t="n">
         <v>45870</v>
       </c>
       <c r="B57" t="n">
@@ -31976,7 +32122,7 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="3" t="n">
+      <c r="A58" s="2" t="n">
         <v>45901</v>
       </c>
       <c r="B58" t="n">
@@ -32002,7 +32148,7 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="3" t="n">
+      <c r="A59" s="2" t="n">
         <v>45931</v>
       </c>
       <c r="B59" t="n">
@@ -32028,7 +32174,7 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="3" t="n">
+      <c r="A60" s="2" t="n">
         <v>45962</v>
       </c>
       <c r="B60" t="n">
@@ -32054,7 +32200,7 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="3" t="n">
+      <c r="A61" s="2" t="n">
         <v>45992</v>
       </c>
       <c r="B61" t="n">
@@ -32080,7 +32226,7 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="3" t="n">
+      <c r="A62" s="2" t="n">
         <v>46023</v>
       </c>
       <c r="B62" t="n">
@@ -32106,7 +32252,7 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="3" t="n">
+      <c r="A63" s="2" t="n">
         <v>46054</v>
       </c>
       <c r="B63" t="n">
@@ -32132,7 +32278,7 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="3" t="n">
+      <c r="A64" s="2" t="n">
         <v>46082</v>
       </c>
       <c r="B64" t="n">
@@ -32158,7 +32304,7 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="3" t="n">
+      <c r="A65" s="2" t="n">
         <v>46113</v>
       </c>
       <c r="B65" t="n">
@@ -32244,7 +32390,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="3" t="n">
+      <c r="A2" s="2" t="n">
         <v>44197</v>
       </c>
       <c r="B2" t="n">
@@ -32270,7 +32416,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="n">
+      <c r="A3" s="2" t="n">
         <v>44228</v>
       </c>
       <c r="B3" t="n">
@@ -32296,7 +32442,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="3" t="n">
+      <c r="A4" s="2" t="n">
         <v>44256</v>
       </c>
       <c r="B4" t="n">
@@ -32322,7 +32468,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="3" t="n">
+      <c r="A5" s="2" t="n">
         <v>44287</v>
       </c>
       <c r="B5" t="n">
@@ -32348,7 +32494,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="3" t="n">
+      <c r="A6" s="2" t="n">
         <v>44317</v>
       </c>
       <c r="B6" t="n">
@@ -32374,7 +32520,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="3" t="n">
+      <c r="A7" s="2" t="n">
         <v>44348</v>
       </c>
       <c r="B7" t="n">
@@ -32400,7 +32546,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="3" t="n">
+      <c r="A8" s="2" t="n">
         <v>44378</v>
       </c>
       <c r="B8" t="n">
@@ -32426,7 +32572,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="3" t="n">
+      <c r="A9" s="2" t="n">
         <v>44409</v>
       </c>
       <c r="B9" t="n">
@@ -32452,7 +32598,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="3" t="n">
+      <c r="A10" s="2" t="n">
         <v>44440</v>
       </c>
       <c r="B10" t="n">
@@ -32478,7 +32624,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="3" t="n">
+      <c r="A11" s="2" t="n">
         <v>44470</v>
       </c>
       <c r="B11" t="n">
@@ -32504,7 +32650,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="3" t="n">
+      <c r="A12" s="2" t="n">
         <v>44501</v>
       </c>
       <c r="B12" t="n">
@@ -32530,7 +32676,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="3" t="n">
+      <c r="A13" s="2" t="n">
         <v>44531</v>
       </c>
       <c r="B13" t="n">
@@ -32556,7 +32702,7 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="3" t="n">
+      <c r="A14" s="2" t="n">
         <v>44562</v>
       </c>
       <c r="B14" t="n">
@@ -32582,7 +32728,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="3" t="n">
+      <c r="A15" s="2" t="n">
         <v>44593</v>
       </c>
       <c r="B15" t="n">
@@ -32608,7 +32754,7 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="3" t="n">
+      <c r="A16" s="2" t="n">
         <v>44621</v>
       </c>
       <c r="B16" t="n">
@@ -32634,7 +32780,7 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="3" t="n">
+      <c r="A17" s="2" t="n">
         <v>44652</v>
       </c>
       <c r="B17" t="n">
@@ -32660,7 +32806,7 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="3" t="n">
+      <c r="A18" s="2" t="n">
         <v>44682</v>
       </c>
       <c r="B18" t="n">
@@ -32686,7 +32832,7 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="3" t="n">
+      <c r="A19" s="2" t="n">
         <v>44713</v>
       </c>
       <c r="B19" t="n">
@@ -32712,7 +32858,7 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="3" t="n">
+      <c r="A20" s="2" t="n">
         <v>44743</v>
       </c>
       <c r="B20" t="n">
@@ -32738,7 +32884,7 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="3" t="n">
+      <c r="A21" s="2" t="n">
         <v>44774</v>
       </c>
       <c r="B21" t="n">
@@ -32764,7 +32910,7 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="3" t="n">
+      <c r="A22" s="2" t="n">
         <v>44805</v>
       </c>
       <c r="B22" t="n">
@@ -32790,7 +32936,7 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="3" t="n">
+      <c r="A23" s="2" t="n">
         <v>44835</v>
       </c>
       <c r="B23" t="n">
@@ -32816,7 +32962,7 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="3" t="n">
+      <c r="A24" s="2" t="n">
         <v>44866</v>
       </c>
       <c r="B24" t="n">
@@ -32842,7 +32988,7 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="3" t="n">
+      <c r="A25" s="2" t="n">
         <v>44896</v>
       </c>
       <c r="B25" t="n">
@@ -32868,7 +33014,7 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="3" t="n">
+      <c r="A26" s="2" t="n">
         <v>44927</v>
       </c>
       <c r="B26" t="n">
@@ -32894,7 +33040,7 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="3" t="n">
+      <c r="A27" s="2" t="n">
         <v>44958</v>
       </c>
       <c r="B27" t="n">
@@ -32920,7 +33066,7 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="3" t="n">
+      <c r="A28" s="2" t="n">
         <v>44986</v>
       </c>
       <c r="B28" t="n">
@@ -32946,7 +33092,7 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="3" t="n">
+      <c r="A29" s="2" t="n">
         <v>45017</v>
       </c>
       <c r="B29" t="n">
@@ -32972,7 +33118,7 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="3" t="n">
+      <c r="A30" s="2" t="n">
         <v>45047</v>
       </c>
       <c r="B30" t="n">
@@ -32998,7 +33144,7 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="3" t="n">
+      <c r="A31" s="2" t="n">
         <v>45078</v>
       </c>
       <c r="B31" t="n">
@@ -33024,7 +33170,7 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="3" t="n">
+      <c r="A32" s="2" t="n">
         <v>45108</v>
       </c>
       <c r="B32" t="n">
@@ -33050,7 +33196,7 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="3" t="n">
+      <c r="A33" s="2" t="n">
         <v>45139</v>
       </c>
       <c r="B33" t="n">
@@ -33076,7 +33222,7 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="3" t="n">
+      <c r="A34" s="2" t="n">
         <v>45170</v>
       </c>
       <c r="B34" t="n">
@@ -33102,7 +33248,7 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="3" t="n">
+      <c r="A35" s="2" t="n">
         <v>45200</v>
       </c>
       <c r="B35" t="n">
@@ -33128,7 +33274,7 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="3" t="n">
+      <c r="A36" s="2" t="n">
         <v>45231</v>
       </c>
       <c r="B36" t="n">
@@ -33154,7 +33300,7 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="3" t="n">
+      <c r="A37" s="2" t="n">
         <v>45261</v>
       </c>
       <c r="B37" t="n">
@@ -33180,7 +33326,7 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="3" t="n">
+      <c r="A38" s="2" t="n">
         <v>45292</v>
       </c>
       <c r="B38" t="n">
@@ -33206,7 +33352,7 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="3" t="n">
+      <c r="A39" s="2" t="n">
         <v>45323</v>
       </c>
       <c r="B39" t="n">
@@ -33232,7 +33378,7 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="3" t="n">
+      <c r="A40" s="2" t="n">
         <v>45352</v>
       </c>
       <c r="B40" t="n">
@@ -33258,7 +33404,7 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="3" t="n">
+      <c r="A41" s="2" t="n">
         <v>45383</v>
       </c>
       <c r="B41" t="n">
@@ -33284,7 +33430,7 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="3" t="n">
+      <c r="A42" s="2" t="n">
         <v>45413</v>
       </c>
       <c r="B42" t="n">
@@ -33310,7 +33456,7 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="3" t="n">
+      <c r="A43" s="2" t="n">
         <v>45444</v>
       </c>
       <c r="B43" t="n">
@@ -33336,7 +33482,7 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="3" t="n">
+      <c r="A44" s="2" t="n">
         <v>45474</v>
       </c>
       <c r="B44" t="n">
@@ -33362,7 +33508,7 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="3" t="n">
+      <c r="A45" s="2" t="n">
         <v>45505</v>
       </c>
       <c r="B45" t="n">
@@ -33388,7 +33534,7 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="3" t="n">
+      <c r="A46" s="2" t="n">
         <v>45536</v>
       </c>
       <c r="B46" t="n">
@@ -33414,7 +33560,7 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="3" t="n">
+      <c r="A47" s="2" t="n">
         <v>45566</v>
       </c>
       <c r="B47" t="n">
@@ -33440,7 +33586,7 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="3" t="n">
+      <c r="A48" s="2" t="n">
         <v>45597</v>
       </c>
       <c r="B48" t="n">
@@ -33466,7 +33612,7 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="3" t="n">
+      <c r="A49" s="2" t="n">
         <v>45627</v>
       </c>
       <c r="B49" t="n">
@@ -33492,7 +33638,7 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="3" t="n">
+      <c r="A50" s="2" t="n">
         <v>45658</v>
       </c>
       <c r="B50" t="n">
@@ -33518,7 +33664,7 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="3" t="n">
+      <c r="A51" s="2" t="n">
         <v>45689</v>
       </c>
       <c r="B51" t="n">
@@ -33544,7 +33690,7 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="3" t="n">
+      <c r="A52" s="2" t="n">
         <v>45717</v>
       </c>
       <c r="B52" t="n">
@@ -33570,7 +33716,7 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="3" t="n">
+      <c r="A53" s="2" t="n">
         <v>45748</v>
       </c>
       <c r="B53" t="n">
@@ -33596,7 +33742,7 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="3" t="n">
+      <c r="A54" s="2" t="n">
         <v>45778</v>
       </c>
       <c r="B54" t="n">
@@ -33622,7 +33768,7 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="3" t="n">
+      <c r="A55" s="2" t="n">
         <v>45809</v>
       </c>
       <c r="B55" t="n">
@@ -33648,7 +33794,7 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="3" t="n">
+      <c r="A56" s="2" t="n">
         <v>45839</v>
       </c>
       <c r="B56" t="n">
@@ -33674,7 +33820,7 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="3" t="n">
+      <c r="A57" s="2" t="n">
         <v>45870</v>
       </c>
       <c r="B57" t="n">
@@ -33700,7 +33846,7 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="3" t="n">
+      <c r="A58" s="2" t="n">
         <v>45901</v>
       </c>
       <c r="B58" t="n">
@@ -33726,7 +33872,7 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="3" t="n">
+      <c r="A59" s="2" t="n">
         <v>45931</v>
       </c>
       <c r="B59" t="n">
@@ -33752,7 +33898,7 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="3" t="n">
+      <c r="A60" s="2" t="n">
         <v>45962</v>
       </c>
       <c r="B60" t="n">
@@ -33778,7 +33924,7 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="3" t="n">
+      <c r="A61" s="2" t="n">
         <v>45992</v>
       </c>
       <c r="B61" t="n">
@@ -33804,7 +33950,7 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="3" t="n">
+      <c r="A62" s="2" t="n">
         <v>46023</v>
       </c>
       <c r="B62" t="n">
@@ -33830,7 +33976,7 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="3" t="n">
+      <c r="A63" s="2" t="n">
         <v>46054</v>
       </c>
       <c r="B63" t="n">
@@ -33856,7 +34002,7 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="3" t="n">
+      <c r="A64" s="2" t="n">
         <v>46082</v>
       </c>
       <c r="B64" t="n">
@@ -33882,7 +34028,7 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="3" t="n">
+      <c r="A65" s="2" t="n">
         <v>46113</v>
       </c>
       <c r="B65" t="n">
@@ -33908,7 +34054,7 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="3" t="n">
+      <c r="A66" s="2" t="n">
         <v>46143</v>
       </c>
       <c r="B66" t="n">
@@ -33994,7 +34140,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="3" t="n">
+      <c r="A2" s="2" t="n">
         <v>44197</v>
       </c>
       <c r="B2" t="n">
@@ -34020,7 +34166,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="n">
+      <c r="A3" s="2" t="n">
         <v>44228</v>
       </c>
       <c r="B3" t="n">
@@ -34046,7 +34192,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="3" t="n">
+      <c r="A4" s="2" t="n">
         <v>44256</v>
       </c>
       <c r="B4" t="n">
@@ -34072,7 +34218,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="3" t="n">
+      <c r="A5" s="2" t="n">
         <v>44287</v>
       </c>
       <c r="B5" t="n">
@@ -34098,7 +34244,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="3" t="n">
+      <c r="A6" s="2" t="n">
         <v>44317</v>
       </c>
       <c r="B6" t="n">
@@ -34124,7 +34270,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="3" t="n">
+      <c r="A7" s="2" t="n">
         <v>44348</v>
       </c>
       <c r="B7" t="n">
@@ -34150,7 +34296,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="3" t="n">
+      <c r="A8" s="2" t="n">
         <v>44378</v>
       </c>
       <c r="B8" t="n">
@@ -34176,7 +34322,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="3" t="n">
+      <c r="A9" s="2" t="n">
         <v>44409</v>
       </c>
       <c r="B9" t="n">
@@ -34202,7 +34348,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="3" t="n">
+      <c r="A10" s="2" t="n">
         <v>44440</v>
       </c>
       <c r="B10" t="n">
@@ -34228,7 +34374,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="3" t="n">
+      <c r="A11" s="2" t="n">
         <v>44470</v>
       </c>
       <c r="B11" t="n">
@@ -34254,7 +34400,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="3" t="n">
+      <c r="A12" s="2" t="n">
         <v>44501</v>
       </c>
       <c r="B12" t="n">
@@ -34280,7 +34426,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="3" t="n">
+      <c r="A13" s="2" t="n">
         <v>44531</v>
       </c>
       <c r="B13" t="n">
@@ -34306,7 +34452,7 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="3" t="n">
+      <c r="A14" s="2" t="n">
         <v>44562</v>
       </c>
       <c r="B14" t="n">
@@ -34332,7 +34478,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="3" t="n">
+      <c r="A15" s="2" t="n">
         <v>44593</v>
       </c>
       <c r="B15" t="n">
@@ -34358,7 +34504,7 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="3" t="n">
+      <c r="A16" s="2" t="n">
         <v>44621</v>
       </c>
       <c r="B16" t="n">
@@ -34384,7 +34530,7 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="3" t="n">
+      <c r="A17" s="2" t="n">
         <v>44652</v>
       </c>
       <c r="B17" t="n">
@@ -34410,7 +34556,7 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="3" t="n">
+      <c r="A18" s="2" t="n">
         <v>44682</v>
       </c>
       <c r="B18" t="n">
@@ -34436,7 +34582,7 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="3" t="n">
+      <c r="A19" s="2" t="n">
         <v>44713</v>
       </c>
       <c r="B19" t="n">
@@ -34462,7 +34608,7 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="3" t="n">
+      <c r="A20" s="2" t="n">
         <v>44743</v>
       </c>
       <c r="B20" t="n">
@@ -34488,7 +34634,7 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="3" t="n">
+      <c r="A21" s="2" t="n">
         <v>44774</v>
       </c>
       <c r="B21" t="n">
@@ -34514,7 +34660,7 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="3" t="n">
+      <c r="A22" s="2" t="n">
         <v>44805</v>
       </c>
       <c r="B22" t="n">
@@ -34540,7 +34686,7 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="3" t="n">
+      <c r="A23" s="2" t="n">
         <v>44835</v>
       </c>
       <c r="B23" t="n">
@@ -34566,7 +34712,7 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="3" t="n">
+      <c r="A24" s="2" t="n">
         <v>44866</v>
       </c>
       <c r="B24" t="n">
@@ -34592,7 +34738,7 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="3" t="n">
+      <c r="A25" s="2" t="n">
         <v>44896</v>
       </c>
       <c r="B25" t="n">
@@ -34618,7 +34764,7 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="3" t="n">
+      <c r="A26" s="2" t="n">
         <v>44927</v>
       </c>
       <c r="B26" t="n">
@@ -34644,7 +34790,7 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="3" t="n">
+      <c r="A27" s="2" t="n">
         <v>44958</v>
       </c>
       <c r="B27" t="n">
@@ -34670,7 +34816,7 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="3" t="n">
+      <c r="A28" s="2" t="n">
         <v>44986</v>
       </c>
       <c r="B28" t="n">
@@ -34696,7 +34842,7 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="3" t="n">
+      <c r="A29" s="2" t="n">
         <v>45017</v>
       </c>
       <c r="B29" t="n">
@@ -34722,7 +34868,7 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="3" t="n">
+      <c r="A30" s="2" t="n">
         <v>45047</v>
       </c>
       <c r="B30" t="n">
@@ -34748,7 +34894,7 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="3" t="n">
+      <c r="A31" s="2" t="n">
         <v>45078</v>
       </c>
       <c r="B31" t="n">
@@ -34774,7 +34920,7 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="3" t="n">
+      <c r="A32" s="2" t="n">
         <v>45108</v>
       </c>
       <c r="B32" t="n">
@@ -34800,7 +34946,7 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="3" t="n">
+      <c r="A33" s="2" t="n">
         <v>45139</v>
       </c>
       <c r="B33" t="n">
@@ -34826,7 +34972,7 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="3" t="n">
+      <c r="A34" s="2" t="n">
         <v>45170</v>
       </c>
       <c r="B34" t="n">
@@ -34852,7 +34998,7 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="3" t="n">
+      <c r="A35" s="2" t="n">
         <v>45200</v>
       </c>
       <c r="B35" t="n">
@@ -34878,7 +35024,7 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="3" t="n">
+      <c r="A36" s="2" t="n">
         <v>45231</v>
       </c>
       <c r="B36" t="n">
@@ -34904,7 +35050,7 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="3" t="n">
+      <c r="A37" s="2" t="n">
         <v>45261</v>
       </c>
       <c r="B37" t="n">
@@ -34930,7 +35076,7 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="3" t="n">
+      <c r="A38" s="2" t="n">
         <v>45292</v>
       </c>
       <c r="B38" t="n">
@@ -34956,7 +35102,7 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="3" t="n">
+      <c r="A39" s="2" t="n">
         <v>45323</v>
       </c>
       <c r="B39" t="n">
@@ -34982,7 +35128,7 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="3" t="n">
+      <c r="A40" s="2" t="n">
         <v>45352</v>
       </c>
       <c r="B40" t="n">
@@ -35008,7 +35154,7 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="3" t="n">
+      <c r="A41" s="2" t="n">
         <v>45383</v>
       </c>
       <c r="B41" t="n">
@@ -35034,7 +35180,7 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="3" t="n">
+      <c r="A42" s="2" t="n">
         <v>45413</v>
       </c>
       <c r="B42" t="n">
@@ -35060,7 +35206,7 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="3" t="n">
+      <c r="A43" s="2" t="n">
         <v>45444</v>
       </c>
       <c r="B43" t="n">
@@ -35086,7 +35232,7 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="3" t="n">
+      <c r="A44" s="2" t="n">
         <v>45474</v>
       </c>
       <c r="B44" t="n">
@@ -35112,7 +35258,7 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="3" t="n">
+      <c r="A45" s="2" t="n">
         <v>45505</v>
       </c>
       <c r="B45" t="n">
@@ -35138,7 +35284,7 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="3" t="n">
+      <c r="A46" s="2" t="n">
         <v>45536</v>
       </c>
       <c r="B46" t="n">
@@ -35164,7 +35310,7 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="3" t="n">
+      <c r="A47" s="2" t="n">
         <v>45566</v>
       </c>
       <c r="B47" t="n">
@@ -35190,7 +35336,7 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="3" t="n">
+      <c r="A48" s="2" t="n">
         <v>45597</v>
       </c>
       <c r="B48" t="n">
@@ -35216,7 +35362,7 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="3" t="n">
+      <c r="A49" s="2" t="n">
         <v>45627</v>
       </c>
       <c r="B49" t="n">
@@ -35242,7 +35388,7 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="3" t="n">
+      <c r="A50" s="2" t="n">
         <v>45658</v>
       </c>
       <c r="B50" t="n">
@@ -35268,7 +35414,7 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="3" t="n">
+      <c r="A51" s="2" t="n">
         <v>45689</v>
       </c>
       <c r="B51" t="n">
@@ -35294,7 +35440,7 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="3" t="n">
+      <c r="A52" s="2" t="n">
         <v>45717</v>
       </c>
       <c r="B52" t="n">
@@ -35320,7 +35466,7 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="3" t="n">
+      <c r="A53" s="2" t="n">
         <v>45748</v>
       </c>
       <c r="B53" t="n">
@@ -35346,7 +35492,7 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="3" t="n">
+      <c r="A54" s="2" t="n">
         <v>45778</v>
       </c>
       <c r="B54" t="n">
@@ -35372,7 +35518,7 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="3" t="n">
+      <c r="A55" s="2" t="n">
         <v>45809</v>
       </c>
       <c r="B55" t="n">
@@ -35398,7 +35544,7 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="3" t="n">
+      <c r="A56" s="2" t="n">
         <v>45839</v>
       </c>
       <c r="B56" t="n">
@@ -35424,7 +35570,7 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="3" t="n">
+      <c r="A57" s="2" t="n">
         <v>45870</v>
       </c>
       <c r="B57" t="n">
@@ -35450,7 +35596,7 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="3" t="n">
+      <c r="A58" s="2" t="n">
         <v>45901</v>
       </c>
       <c r="B58" t="n">
@@ -35476,7 +35622,7 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="3" t="n">
+      <c r="A59" s="2" t="n">
         <v>45931</v>
       </c>
       <c r="B59" t="n">
@@ -35502,7 +35648,7 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="3" t="n">
+      <c r="A60" s="2" t="n">
         <v>45962</v>
       </c>
       <c r="B60" t="n">
@@ -35528,7 +35674,7 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="3" t="n">
+      <c r="A61" s="2" t="n">
         <v>45992</v>
       </c>
       <c r="B61" t="n">
@@ -35554,7 +35700,7 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="3" t="n">
+      <c r="A62" s="2" t="n">
         <v>46023</v>
       </c>
       <c r="B62" t="n">
@@ -35580,7 +35726,7 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="3" t="n">
+      <c r="A63" s="2" t="n">
         <v>46054</v>
       </c>
       <c r="B63" t="n">
@@ -35606,7 +35752,7 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="3" t="n">
+      <c r="A64" s="2" t="n">
         <v>46082</v>
       </c>
       <c r="B64" t="n">
@@ -35632,7 +35778,7 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="3" t="n">
+      <c r="A65" s="2" t="n">
         <v>46113</v>
       </c>
       <c r="B65" t="n">
@@ -35658,7 +35804,7 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="3" t="n">
+      <c r="A66" s="2" t="n">
         <v>46143</v>
       </c>
       <c r="B66" t="n">
@@ -35684,7 +35830,7 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="3" t="n">
+      <c r="A67" s="2" t="n">
         <v>46174</v>
       </c>
       <c r="B67" t="n">

--- a/output/Data and Chart Outputs/south_america_power_by_type.xlsx
+++ b/output/Data and Chart Outputs/south_america_power_by_type.xlsx
@@ -166,6 +166,7 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
+              <a:rPr sz="1200" b="1"/>
               <a:t>Argentina power generation by type (to May/26)</a:t>
             </a:r>
           </a:p>
@@ -469,6 +470,7 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
+              <a:rPr sz="1200" b="1"/>
               <a:t>Bolivia power generation by type (to May/26)</a:t>
             </a:r>
           </a:p>
@@ -772,6 +774,7 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
+              <a:rPr sz="1200" b="1"/>
               <a:t>Brazil power generation by type (to Apr/26)</a:t>
             </a:r>
           </a:p>
@@ -1075,6 +1078,7 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
+              <a:rPr sz="1200" b="1"/>
               <a:t>Chile power generation by type (to Apr/26)</a:t>
             </a:r>
           </a:p>
@@ -1378,6 +1382,7 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
+              <a:rPr sz="1200" b="1"/>
               <a:t>Colombia power generation by type (to Dec/25)</a:t>
             </a:r>
           </a:p>
@@ -1681,6 +1686,7 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
+              <a:rPr sz="1200" b="1"/>
               <a:t>Ecuador power generation by type (to Apr/26)</a:t>
             </a:r>
           </a:p>
@@ -1984,6 +1990,7 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
+              <a:rPr sz="1200" b="1"/>
               <a:t>Peru power generation by type (to May/26)</a:t>
             </a:r>
           </a:p>
@@ -2287,6 +2294,7 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
+              <a:rPr sz="1200" b="1"/>
               <a:t>Uruguay power generation by type (to Jun/26)</a:t>
             </a:r>
           </a:p>
@@ -3128,7 +3136,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Monthly. Argentina: 2021-01 to 2026-05; Bolivia: 2021-01 to 2026-05; Brazil: 2021-01 to 2026-04; Chile: 2021-01 to 2026-04; Colombia: 2021-01 to 2025-12; Ecuador: 2021-01 to 2026-04; Peru: 2021-01 to 2026-05; Uruguay: 2021-01 to 2026-06. Ember lags real time by one to several months (it varies by country); the weekly run picks up new months as they're released.</t>
+          <t>Monthly. Argentina: 2021-01 to 2026-05; Bolivia: 2021-01 to 2026-05; Brazil: 2021-01 to 2026-04; Chile: 2021-01 to 2026-04; Colombia: 2021-01 to 2025-12; Ecuador: 2021-01 to 2026-04; Peru: 2021-01 to 2026-05; Uruguay: 2021-01 to 2026-06. Ember lags real time by one to several months (it varies by country); each scheduled run picks up new months as they're released.</t>
         </is>
       </c>
     </row>
